--- a/Data_Model_Class_Words_ColumnName_Standards.xlsx
+++ b/Data_Model_Class_Words_ColumnName_Standards.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a059361\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C27E7FE-C9AE-454B-845A-B47C240B5E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10387CB1-0BDD-457D-8257-2803679B3103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{559F7F44-CE42-4D1B-81C6-F57E859E529E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ClassWords" sheetId="1" r:id="rId1"/>
+    <sheet name="ClassWords and 5 part naming" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
   <si>
     <t>S.No</t>
   </si>
@@ -274,6 +274,72 @@
   </si>
   <si>
     <t>123A-123</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Transaction_Count</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Entity Qualifier</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>ClassWord</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>5 Part Naming Convention</t>
+  </si>
+  <si>
+    <t>Coumn Name</t>
+  </si>
+  <si>
+    <t>Home_Prod_Min_Sale_Amt</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>Policy_Cust_First_Name</t>
+  </si>
+  <si>
+    <t>LOB</t>
+  </si>
+  <si>
+    <t>LOB_Code</t>
+  </si>
+  <si>
+    <t>Attribute\Classword Qualifier</t>
+  </si>
+  <si>
+    <t>Executed</t>
+  </si>
+  <si>
+    <t>Transaction</t>
+  </si>
+  <si>
+    <t>Transaction_Exec_Date</t>
   </si>
 </sst>
 </file>
@@ -300,12 +366,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -335,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -344,6 +416,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -678,14 +755,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85F26F5-7356-4F6C-8CFA-B728104E02EF}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -950,7 +1032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -967,7 +1049,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -984,7 +1066,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1001,7 +1083,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1018,7 +1100,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1035,7 +1117,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1052,7 +1134,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1069,7 +1151,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1085,11 +1167,163 @@
       <c r="E24" s="2" t="s">
         <v>67</v>
       </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="8">
+        <v>10</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>1</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>2</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>3</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E27">
     <sortCondition ref="B2:B27"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Data_Model_Class_Words_ColumnName_Standards.xlsx
+++ b/Data_Model_Class_Words_ColumnName_Standards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a059361\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10387CB1-0BDD-457D-8257-2803679B3103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90F2CB6-7FBC-4375-BFE2-C381291E743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{559F7F44-CE42-4D1B-81C6-F57E859E529E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="105">
   <si>
     <t>S.No</t>
   </si>
@@ -80,10 +80,6 @@
     <t>Blob</t>
   </si>
   <si>
-    <t>Policy_Blob
-Claim_Image_Blob</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -340,6 +336,21 @@
   </si>
   <si>
     <t>Transaction_Exec_Date</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <t>Unit of Measure</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Policy_Amount_UOM</t>
+  </si>
+  <si>
+    <t>Claim_Image_Blob</t>
   </si>
 </sst>
 </file>
@@ -755,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F85F26F5-7356-4F6C-8CFA-B728104E02EF}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
@@ -804,7 +815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -812,11 +823,11 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -824,16 +835,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -841,16 +852,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -858,7 +869,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
@@ -867,24 +878,24 @@
         <v>100</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>66</v>
+      <c r="B7" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="8">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -892,16 +903,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -909,16 +920,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -926,16 +937,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -943,12 +954,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -956,16 +971,12 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -973,16 +984,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1234</v>
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -990,16 +1001,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>6</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1234</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1007,12 +1018,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1020,16 +1035,12 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1234</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1037,16 +1048,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>74</v>
+        <v>40</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1234</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1054,16 +1065,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1071,16 +1082,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1234</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1088,16 +1099,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D20" s="2">
         <v>1234</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1105,16 +1116,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>1234</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1122,16 +1133,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>76</v>
+      <c r="D22" s="2">
+        <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1139,16 +1150,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.50070601851851848</v>
+        <v>58</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1156,16 +1167,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.50070601851851848</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1173,156 +1184,173 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="8">
+        <v>101</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="F30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="9"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
         <v>1</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6" t="s">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>2</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>3</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
+        <v>3</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>4</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E27">
-    <sortCondition ref="B2:B27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E26">
+    <sortCondition ref="B2:B26"/>
   </sortState>
   <mergeCells count="1">
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
